--- a/research/traditional_assets/database/data/singapore/singapore_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_software_entertainment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.6186802677717566</v>
+        <v>-0.3436883007771476</v>
       </c>
       <c r="H2">
-        <v>-0.6651790457974711</v>
+        <v>-0.4279563116992229</v>
       </c>
       <c r="I2">
-        <v>0.307338453824873</v>
+        <v>-0.2860051874061029</v>
       </c>
       <c r="J2">
-        <v>0.307338453824873</v>
+        <v>-0.2860051874061029</v>
       </c>
       <c r="K2">
-        <v>-148.6</v>
+        <v>-119.2</v>
       </c>
       <c r="L2">
-        <v>-1.579003294017639</v>
+        <v>-0.6259189245956732</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.000952621566995601</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.00537751677852349</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,70 +624,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.641</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>259.7</v>
+        <v>240.02</v>
       </c>
       <c r="V2">
-        <v>0.3594463667820069</v>
+        <v>0.3567055046962311</v>
       </c>
       <c r="W2">
-        <v>1.708814718111638</v>
+        <v>-0.7928571428571428</v>
       </c>
       <c r="X2">
-        <v>0.1271086466162184</v>
+        <v>0.1017890133302165</v>
       </c>
       <c r="Y2">
-        <v>1.58170607149542</v>
+        <v>-0.8946461561873593</v>
       </c>
       <c r="Z2">
-        <v>19.68050062265527</v>
+        <v>0.8004707662561472</v>
       </c>
       <c r="AB2">
-        <v>0.1254202689955248</v>
+        <v>0.1009952258592406</v>
       </c>
       <c r="AD2">
-        <v>9.615</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="AE2">
-        <v>0.6018905527060101</v>
+        <v>1.509139448091178</v>
       </c>
       <c r="AF2">
-        <v>10.21689055270601</v>
+        <v>9.591139448091178</v>
       </c>
       <c r="AG2">
-        <v>-249.483109447294</v>
+        <v>-230.4288605519088</v>
       </c>
       <c r="AH2">
-        <v>0.01394384472971432</v>
+        <v>0.0140535458478837</v>
       </c>
       <c r="AI2">
-        <v>0.02031122760406688</v>
+        <v>0.02036516336532774</v>
       </c>
       <c r="AJ2">
-        <v>-0.5274296001476405</v>
+        <v>-0.520800694149739</v>
       </c>
       <c r="AK2">
-        <v>-1.025342338053807</v>
+        <v>-0.9977947388967475</v>
       </c>
       <c r="AL2">
-        <v>0.021</v>
+        <v>6.688</v>
       </c>
       <c r="AM2">
-        <v>-6.437</v>
+        <v>5.23</v>
       </c>
       <c r="AN2">
-        <v>0.2450056059525023</v>
+        <v>-0.1706323234455822</v>
       </c>
       <c r="AO2">
-        <v>1371.428571428571</v>
+        <v>-8.178827751196174</v>
       </c>
       <c r="AP2">
-        <v>-6.357229371299919</v>
+        <v>4.864960636586273</v>
       </c>
       <c r="AQ2">
-        <v>-4.474133913313655</v>
+        <v>-10.45889101338432</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PropertyGuru Limited (NYSE:PGRU)</t>
+          <t>PropertyGuru Group Limited (NYSE:PGRU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,22 +710,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.3031973539140022</v>
+        <v>-0.1272727272727273</v>
       </c>
       <c r="H3">
-        <v>-0.350606394707828</v>
+        <v>-0.2102846648301193</v>
       </c>
       <c r="I3">
-        <v>0.7894156560088202</v>
+        <v>-0.1808999081726354</v>
       </c>
       <c r="J3">
-        <v>0.7894156560088202</v>
+        <v>-0.1808999081726354</v>
       </c>
       <c r="K3">
-        <v>-105.4</v>
+        <v>-15.8</v>
       </c>
       <c r="L3">
-        <v>-1.162072767364939</v>
+        <v>-0.1450872359963269</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,61 +749,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>236.7</v>
+        <v>231.8</v>
       </c>
       <c r="V3">
-        <v>0.3400373509553225</v>
+        <v>0.3883397554029151</v>
       </c>
       <c r="W3">
-        <v>0.6124346310284718</v>
+        <v>-0.03396388650042993</v>
       </c>
       <c r="X3">
-        <v>0.1264951712970453</v>
+        <v>0.1017890133302165</v>
       </c>
       <c r="Y3">
-        <v>0.4859394597314265</v>
+        <v>-0.1357528998306464</v>
+      </c>
+      <c r="Z3">
+        <v>0.4577361187003489</v>
+      </c>
+      <c r="AA3">
+        <v>-0.08280442184019166</v>
       </c>
       <c r="AB3">
-        <v>0.1254589366272246</v>
+        <v>0.1009952258592406</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1837996476994323</v>
       </c>
       <c r="AD3">
-        <v>9.41</v>
+        <v>8.06</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.41</v>
+        <v>8.06</v>
       </c>
       <c r="AG3">
-        <v>-227.29</v>
+        <v>-223.74</v>
       </c>
       <c r="AH3">
-        <v>0.01333786905926209</v>
+        <v>0.01332319492197831</v>
       </c>
       <c r="AI3">
-        <v>0.01982680516634711</v>
+        <v>0.01753469956054475</v>
       </c>
       <c r="AJ3">
-        <v>-0.4848232759540111</v>
+        <v>-0.5995819487619253</v>
       </c>
       <c r="AK3">
-        <v>-0.9553612710688916</v>
+        <v>-0.9819187220222944</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AM3">
-        <v>-6.41</v>
+        <v>-0.952</v>
       </c>
       <c r="AN3">
-        <v>0.1197201017811705</v>
+        <v>-0.5133757961783441</v>
+      </c>
+      <c r="AO3">
+        <v>-63.96103896103896</v>
       </c>
       <c r="AP3">
-        <v>-2.891730279898219</v>
+        <v>14.25095541401274</v>
       </c>
       <c r="AQ3">
-        <v>-11.17004680187207</v>
+        <v>20.69327731092437</v>
       </c>
     </row>
     <row r="4">
@@ -811,121 +826,225 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>MoneyHero Limited (NasdaqGM:MNY)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.3363259668508287</v>
+      </c>
+      <c r="H4">
+        <v>-0.4323204419889503</v>
+      </c>
+      <c r="I4">
+        <v>-0.2058011049723757</v>
+      </c>
+      <c r="J4">
+        <v>-0.2058011049723757</v>
+      </c>
+      <c r="K4">
+        <v>-81.2</v>
+      </c>
+      <c r="L4">
+        <v>-1.121546961325967</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0.1010908837372769</v>
+      </c>
+      <c r="AB4">
+        <v>0.1010908837372769</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>-0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>-0</v>
+      </c>
+      <c r="AL4">
+        <v>6.37</v>
+      </c>
+      <c r="AM4">
+        <v>6.342000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-2.339089481946625</v>
+      </c>
+      <c r="AP4">
+        <v>-0</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.349416587827184</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Society Pass Incorporated (NasdaqCM:SOPA)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Software (Entertainment)</t>
         </is>
       </c>
-      <c r="G4">
-        <v>-9.009970674486803</v>
-      </c>
-      <c r="H4">
-        <v>-9.032258064516128</v>
-      </c>
-      <c r="I4">
-        <v>-12.51506689458686</v>
-      </c>
-      <c r="J4">
-        <v>-12.51506689458686</v>
-      </c>
-      <c r="K4">
-        <v>-43.2</v>
-      </c>
-      <c r="L4">
-        <v>-12.66862170087977</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>23</v>
-      </c>
-      <c r="V4">
-        <v>0.8712121212121212</v>
-      </c>
-      <c r="W4">
-        <v>2.805194805194805</v>
-      </c>
-      <c r="X4">
-        <v>0.1277221219353915</v>
-      </c>
-      <c r="Y4">
-        <v>2.677472683259414</v>
-      </c>
-      <c r="Z4">
-        <v>0.7131070781346773</v>
-      </c>
-      <c r="AA4">
-        <v>-8.924582785858867</v>
-      </c>
-      <c r="AB4">
-        <v>0.125381601363825</v>
-      </c>
-      <c r="AC4">
-        <v>-9.049964387222692</v>
-      </c>
-      <c r="AD4">
-        <v>0.205</v>
-      </c>
-      <c r="AE4">
-        <v>0.6018905527060101</v>
-      </c>
-      <c r="AF4">
-        <v>0.8068905527060101</v>
-      </c>
-      <c r="AG4">
-        <v>-22.19310944729399</v>
-      </c>
-      <c r="AH4">
-        <v>0.02965758071996053</v>
-      </c>
-      <c r="AI4">
-        <v>0.02840474747522645</v>
-      </c>
-      <c r="AJ4">
-        <v>-5.275418784788363</v>
-      </c>
-      <c r="AK4">
-        <v>-4.104597500348309</v>
-      </c>
-      <c r="AL4">
-        <v>0.021</v>
-      </c>
-      <c r="AM4">
-        <v>-0.027</v>
-      </c>
-      <c r="AN4">
-        <v>-0.005208862689297693</v>
-      </c>
-      <c r="AO4">
-        <v>-2038.095238095238</v>
-      </c>
-      <c r="AP4">
-        <v>0.5639066329732185</v>
-      </c>
-      <c r="AQ4">
-        <v>1585.185185185185</v>
+      <c r="G5">
+        <v>-2.980525164113785</v>
+      </c>
+      <c r="H5">
+        <v>-2.986870897155361</v>
+      </c>
+      <c r="I5">
+        <v>-2.173613554662826</v>
+      </c>
+      <c r="J5">
+        <v>-2.173613554662826</v>
+      </c>
+      <c r="K5">
+        <v>-22.2</v>
+      </c>
+      <c r="L5">
+        <v>-2.428884026258205</v>
+      </c>
+      <c r="M5">
+        <v>0.641</v>
+      </c>
+      <c r="N5">
+        <v>0.06621900826446281</v>
+      </c>
+      <c r="O5">
+        <v>-0.02887387387387387</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0.641</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0.8491735537190084</v>
+      </c>
+      <c r="W5">
+        <v>-0.7928571428571428</v>
+      </c>
+      <c r="X5">
+        <v>0.1092687870800127</v>
+      </c>
+      <c r="Y5">
+        <v>-0.9021259299371556</v>
+      </c>
+      <c r="AB5">
+        <v>0.1001103165593697</v>
+      </c>
+      <c r="AD5">
+        <v>0.022</v>
+      </c>
+      <c r="AE5">
+        <v>1.509139448091178</v>
+      </c>
+      <c r="AF5">
+        <v>1.531139448091178</v>
+      </c>
+      <c r="AG5">
+        <v>-6.688860551908823</v>
+      </c>
+      <c r="AH5">
+        <v>0.1365730446205334</v>
+      </c>
+      <c r="AI5">
+        <v>0.1333612796024127</v>
+      </c>
+      <c r="AJ5">
+        <v>-2.236224912943253</v>
+      </c>
+      <c r="AK5">
+        <v>-2.051080813432855</v>
+      </c>
+      <c r="AL5">
+        <v>0.01</v>
+      </c>
+      <c r="AM5">
+        <v>-0.16</v>
+      </c>
+      <c r="AN5">
+        <v>-0.001245400509482027</v>
+      </c>
+      <c r="AO5">
+        <v>-2010</v>
+      </c>
+      <c r="AP5">
+        <v>0.3786504699637036</v>
+      </c>
+      <c r="AQ5">
+        <v>125.625</v>
       </c>
     </row>
   </sheetData>
